--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/olderyoungersister.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/olderyoungersister.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">What's up, #brother2? </t>
+          <t xml:space="preserve">Que foi, #brother2? </t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">I want you to change your hairstyle. </t>
+          <t xml:space="preserve">Quero que você mude seu penteado. </t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes♪ Does this hairstyle suit me, #brother2? </t>
+          <t xml:space="preserve">Sim♪ Este penteado cai bem em mim, #brother2? </t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">#brother2? Are you really my #brother2? </t>
+          <t xml:space="preserve">#brother2? Você é mesmo meu #brother2? </t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Sim.</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buzzz! Resposta errada.  </t>
+          <t>Bzzt! Resposta errada.</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Este não é meu verdadeiro #brother2!!  </t>
+          <t xml:space="preserve">Este não é meu #brother2 de verdade!! </t>
         </is>
       </c>
     </row>
@@ -873,9 +873,8 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">O quê, sério...!?  _x000D_
-_x000D_
-Tudo bem então, se você é meu #brother2, vou te fazer algumas perguntas fáceis que você com certeza saberá responder!  </t>
+          <t>Como, sério...!?
+Tá bom então, se você é meu #brother2, vou te dar perguntinhas fáceis que você com certeza sabe responder!</t>
         </is>
       </c>
     </row>
@@ -895,7 +894,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pergunta: Qual delas significa "irmã mais velha ou mais nova"?  </t>
+          <t>Pergunta: Qual deles significa "irmã mais nova mais velha"?</t>
         </is>
       </c>
     </row>
@@ -925,7 +924,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uma irmã biológica mais nova separada no nascimento.  </t>
+          <t>Uma irmã biológica mais nova, separada ao nascer.</t>
         </is>
       </c>
     </row>
@@ -955,7 +954,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uma irmã biológica mais velha separada no nascimento.  </t>
+          <t>Uma irmã biológica mais velha, separada ao nascer.</t>
         </is>
       </c>
     </row>
@@ -985,7 +984,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uma irmã não biológica mais nova separada no nascimento.  </t>
+          <t>Uma irmã não biológica mais nova, separada ao nascer.</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1015,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uma irmã não biológica mais velha separada no nascimento.  </t>
+          <t>Uma irmã não biológica mais velha, separada ao nascer.</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1046,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nenhuma das opções acima está correta.  </t>
+          <t>Nenhuma das anteriores está correta.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1093,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ding-dong. Como esperado do meu #brother2! Agora, vou te fazer a próxima pergunta!  </t>
+          <t>Ding-dong. À altura do meu #brother2! Agora, vem a próxima pergunta!</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1113,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pergunta: O que estou escondendo secretamente no quarto do meu #brother2?  </t>
+          <t xml:space="preserve">Pergunta: O que eu estou escondendo às escondidas no quarto do meu #brother2? </t>
         </is>
       </c>
     </row>
@@ -1144,7 +1143,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lanchinhos de emergência.  </t>
+          <t>Lanches de emergência.</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1173,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Um bentô feito com amor para meu #brother2.  </t>
+          <t>Uma marmita feita com amor para o meu #brother2.</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1203,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uma carta cheia de amor para meu #brother2.  </t>
+          <t>Uma carta cheia de amor para o meu #brother2.</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1233,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uma cápsula do tempo cheia de nossas memórias.  </t>
+          <t>Uma cápsula do tempo cheia das nossas memórias.</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1263,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uma faca de cozinha.  </t>
+          <t>Uma faca de cozinha.</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1294,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nada.  </t>
+          <t>Nada.</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1325,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tudo.  </t>
+          <t>Tudo.</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1372,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ding-dong. Como esperado do meu #brother2! Agora, vou te fazer a próxima pergunta!  </t>
+          <t>Ding-dong. À altura do meu #brother2! Agora, vem a próxima pergunta!</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1392,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pergunta: Qual é o escudo mais forte?  </t>
+          <t>Pergunta: Qual é o escudo mais forte?</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1422,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Um escudo de aço.  </t>
+          <t>Um escudo de aço.</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1452,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Um escudo mágico.  </t>
+          <t>Um escudo mágico.</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1477,12 @@
       </c>
       <c r="J73" s="17" t="inlineStr">
         <is>
-          <t>A rubinus shield.</t>
+          <t>A rubynus shield.</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Um escudo de rubinus.  </t>
+          <t>Um escudo de rubynus.</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1512,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Um escudo de éter.  </t>
+          <t>Um escudo de éter.</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1542,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Um escudo invencível.  </t>
+          <t>Um escudo invencível.</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1573,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">O sorriso de uma irmã mais nova.  </t>
+          <t>O sorriso da irmã mais nova.</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1617,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ding-dong. Como esperado do meu #brother2! Agora, vou te fazer a próxima pergunta!  </t>
+          <t>Ding-dong. À altura do meu #brother2! Agora, vem a próxima pergunta!</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1637,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pergunta: Qual é o meu Putit favorito?  </t>
+          <t>Pergunta: Qual é o meu Putit favorito?</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1667,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Putit comum.  </t>
+          <t>Putit comum.</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1697,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Putit vermelho.  </t>
+          <t>Putit vermelho.</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1727,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Putit de neve.  </t>
+          <t>Putit de neve.</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1757,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Putit de metal.  </t>
+          <t>Putit de metal.</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1787,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Putit rei.  </t>
+          <t>Putit rei.</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1818,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Putit anjo.  </t>
+          <t>Putit anjo.</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1849,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Putit caracol.  </t>
+          <t>Putit caramujo.</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1880,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Putit perdido.  </t>
+          <t>Putit vira-lata.</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1927,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ding-dong. Como esperado do meu #brother2! Agora, a última pergunta!  </t>
+          <t>Ding-dong. À altura do meu #brother2! Agora, a última pergunta!</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1947,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pergunta: O que eu mais quero do meu #brother2?  </t>
+          <t>Pergunta: O que eu mais quero do meu #brother2?</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1977,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passar muito tempo juntos.  </t>
+          <t>Passar muito tempo juntos.</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2007,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estar sempre juntos.  </t>
+          <t>Estar sempre juntos.</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2037,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Que nunca me traia.  </t>
+          <t>Que você nunca me traia.</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2067,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Que faça carinho na minha cabeça.  </t>
+          <t>Fazer cafuné em mim.</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2097,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Que brigue comigo.  </t>
+          <t>Me dar bronca.</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2127,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mesada ilimitada.  </t>
+          <t>Mesada ilimitada.</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2158,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Todas as opções acima.  </t>
+          <t>Todas as anteriores.</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2189,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nenhuma das opções acima está correta.  </t>
+          <t>Nenhuma das anteriores está correta.</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2231,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ding-dong. Como esperado do meu #brother2!  </t>
+          <t>Ding-dong. À altura do meu #brother2!</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2251,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parabéns por acertar todas as perguntas. Agora, me dê minha mesada, #brother2♪  </t>
+          <t>Parabéns por acertar todas as perguntas. Agora, me dá minha mesada, #brother2♪</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2286,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entregar 10.000 Orens.  </t>
+          <t>Entregar 10.000 orens.</t>
         </is>
       </c>
     </row>
@@ -2317,7 +2316,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Não tenho isso comigo agora.  </t>
+          <t>Não tenho comigo agora.</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2343,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uau, eu encontrei meu verdadeiro #brother2!  </t>
+          <t xml:space="preserve">Uau, encontrei meu #brother2 de verdade! </t>
         </is>
       </c>
     </row>
@@ -2403,7 +2402,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eu entendo... então você não era meu verdadeiro #brother2, afinal...  </t>
+          <t xml:space="preserve">Entendi... então você não era meu #brother2 de verdade... </t>
         </is>
       </c>
     </row>
